--- a/file/台電電費.xlsx
+++ b/file/台電電費.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3591BB-23EC-C941-9D59-EA1FF0762C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8DCF2C-C55F-A149-98E9-69D2B3E5EB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12420" yWindow="3160" windowWidth="37160" windowHeight="19360" xr2:uid="{6110A708-3115-BF48-A795-F0D8F68AEE36}"/>
+    <workbookView xWindow="2380" yWindow="1160" windowWidth="37160" windowHeight="19360" xr2:uid="{6110A708-3115-BF48-A795-F0D8F68AEE36}"/>
   </bookViews>
   <sheets>
     <sheet name="Analysis" sheetId="2" r:id="rId1"/>
-    <sheet name="工作表1" sheetId="1" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="48" r:id="rId3"/>
+    <pivotCache cacheId="55" r:id="rId3"/>
+    <pivotCache cacheId="61" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>110/08</t>
   </si>
@@ -282,15 +283,6 @@
     <t>030</t>
   </si>
   <si>
-    <t>031</t>
-  </si>
-  <si>
-    <t>032</t>
-  </si>
-  <si>
-    <t>033</t>
-  </si>
-  <si>
     <t>大公電</t>
   </si>
   <si>
@@ -302,6 +294,14 @@
   </si>
   <si>
     <t>小公電</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>付費年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>付費月</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -310,10 +310,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="180" formatCode="#,##0_ "/>
-    <numFmt numFmtId="181" formatCode="#,##0.0_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.0_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -357,21 +357,45 @@
       <name val="楷體-繁 標準體"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -383,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -396,22 +420,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1">
@@ -427,6 +451,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -930,10 +969,10 @@
                 <c:formatCode>#,##0.0_ </c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>403.2</c:v>
+                  <c:v>201.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>455.8</c:v>
+                  <c:v>227.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>196.3</c:v>
@@ -1164,7 +1203,7 @@
                 <c:formatCode>#,##0.0_ </c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="1">
-                  <c:v>536.20000000000005</c:v>
+                  <c:v>268.10000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>161.80000000000001</c:v>
@@ -1467,7 +1506,907 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[台電電費.xlsx]Analysis!樞紐分析表7</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-TW" altLang="en-US" sz="2400" baseline="0">
+                <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              </a:rPr>
+              <a:t>公共用電費雙月分攤 </a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-TW" sz="2400" baseline="0">
+              <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="diamond"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="square"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$B$47:$B$48</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>大公電</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Analysis!$A$49:$A$61</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="10"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>8</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>109</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>110</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$B$49:$B$61</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0_ </c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>429.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>400.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>224.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>466.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>456</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>388.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>384.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>403.1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>388.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>427.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3CA1-0140-9C7F-77BF82E576C3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Analysis!$C$47:$C$48</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>小公電</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="zh-TW"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Analysis!$A$49:$A$61</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="10"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>8</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>109</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>110</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Analysis!$C$49:$C$61</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.0_ </c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>268.10000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>161.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>107.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>110.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>124.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>129.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>157.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>137.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>146</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3CA1-0140-9C7F-77BF82E576C3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="46"/>
+        <c:overlap val="100"/>
+        <c:axId val="978993535"/>
+        <c:axId val="980804479"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="978993535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="980804479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="980804479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-TW" altLang="en-US" sz="1400" baseline="0">
+                    <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  </a:rPr>
+                  <a:t>雙月公電分攤</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0.0_ " sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="978993535"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="楷體-繁" panose="02010600040101010101" pitchFamily="2" charset="-120"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2010,6 +2949,524 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="298">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2048,13 +3505,49 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65E1610D-F4C5-4C4B-BCB0-F71CB0AC792E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44433.72789814815" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="33" xr:uid="{78376DEF-88A6-1E49-9B91-43A46824E6CD}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44434.236995023151" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="30" xr:uid="{78376DEF-88A6-1E49-9B91-43A46824E6CD}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="B1:I34" sheet="工作表1"/>
+    <worksheetSource ref="B1:I31" sheet="Data"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name="母戶電號" numFmtId="0">
@@ -2063,13 +3556,13 @@
     <cacheField name="期別" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="電費金額" numFmtId="180">
+    <cacheField name="電費金額" numFmtId="176">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3121" maxValue="86082"/>
     </cacheField>
-    <cacheField name="戶數" numFmtId="180">
+    <cacheField name="戶數" numFmtId="176">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="39" maxValue="346"/>
     </cacheField>
-    <cacheField name="分攤金額" numFmtId="181">
+    <cacheField name="分攤金額" numFmtId="177">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="63.9" maxValue="268.10000000000002"/>
     </cacheField>
     <cacheField name="年" numFmtId="0">
@@ -2098,8 +3591,100 @@
       <sharedItems count="4">
         <s v="大公電"/>
         <s v="小公電"/>
+        <s v="08007" u="1"/>
         <s v="00010" u="1"/>
-        <s v="08007" u="1"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Tai-Chung Wang" refreshedDate="44434.24023275463" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="30" xr:uid="{B5CFF7EF-2FE0-0E4F-A7A9-BBEF55C5C853}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:K31" sheet="Data"/>
+  </cacheSource>
+  <cacheFields count="11">
+    <cacheField name="No" numFmtId="49">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="母戶電號" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5787600010" maxValue="5787608007"/>
+    </cacheField>
+    <cacheField name="期別" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="電費金額" numFmtId="176">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3121" maxValue="86082"/>
+    </cacheField>
+    <cacheField name="戶數" numFmtId="176">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="39" maxValue="346"/>
+    </cacheField>
+    <cacheField name="分攤金額" numFmtId="177">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="63.9" maxValue="268.10000000000002" count="30">
+        <n v="201.5"/>
+        <n v="226.4"/>
+        <n v="187.8"/>
+        <n v="200.7"/>
+        <n v="208.4"/>
+        <n v="194.7"/>
+        <n v="198.5"/>
+        <n v="185.7"/>
+        <n v="190.7"/>
+        <n v="197.5"/>
+        <n v="248.7"/>
+        <n v="207.3"/>
+        <n v="242.3"/>
+        <n v="224"/>
+        <n v="63.9"/>
+        <n v="160.5"/>
+        <n v="196.3"/>
+        <n v="204.4"/>
+        <n v="201.6"/>
+        <n v="227.9"/>
+        <n v="146"/>
+        <n v="137.1"/>
+        <n v="157.19999999999999"/>
+        <n v="129.30000000000001"/>
+        <n v="124.6"/>
+        <n v="110.9"/>
+        <n v="107.7"/>
+        <n v="80"/>
+        <n v="161.80000000000001"/>
+        <n v="268.10000000000002"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="年" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="109" maxValue="110"/>
+    </cacheField>
+    <cacheField name="月" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="12"/>
+    </cacheField>
+    <cacheField name="保密電號" numFmtId="0">
+      <sharedItems count="2">
+        <s v="大公電"/>
+        <s v="小公電"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="付費年" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="109" maxValue="110" count="2">
+        <n v="110"/>
+        <n v="109"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="付費月" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="12" count="6">
+        <n v="8"/>
+        <n v="6"/>
+        <n v="4"/>
+        <n v="2"/>
+        <n v="12"/>
+        <n v="10"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -2112,7 +3697,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="33">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
   <r>
     <n v="5787600010"/>
     <s v="110/08"/>
@@ -2291,26 +3876,6 @@
     <n v="204.4"/>
     <x v="1"/>
     <x v="5"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="5787600010"/>
-    <s v="109/01"/>
-    <n v="69772"/>
-    <n v="346"/>
-    <n v="201.6"/>
-    <x v="1"/>
-    <x v="6"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <n v="5787600010"/>
-    <s v="109/02"/>
-    <n v="78864"/>
-    <n v="346"/>
-    <n v="227.9"/>
-    <x v="1"/>
-    <x v="7"/>
     <x v="0"/>
   </r>
   <r>
@@ -2433,28 +3998,633 @@
     <x v="7"/>
     <x v="1"/>
   </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="30">
   <r>
+    <s v="002"/>
+    <n v="5787600010"/>
+    <s v="110/08"/>
+    <n v="69736"/>
+    <n v="346"/>
+    <x v="0"/>
+    <n v="110"/>
+    <n v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="003"/>
+    <n v="5787600010"/>
+    <s v="110/07"/>
+    <n v="78353"/>
+    <n v="346"/>
+    <x v="1"/>
+    <n v="110"/>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="005"/>
+    <n v="5787600010"/>
+    <s v="110/05"/>
+    <n v="65004"/>
+    <n v="346"/>
+    <x v="2"/>
+    <n v="110"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="006"/>
+    <n v="5787600010"/>
+    <s v="110/06"/>
+    <n v="69468"/>
+    <n v="346"/>
+    <x v="3"/>
+    <n v="110"/>
+    <n v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="008"/>
+    <n v="5787600010"/>
+    <s v="110/03"/>
+    <n v="71923"/>
+    <n v="345"/>
+    <x v="4"/>
+    <n v="110"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="009"/>
+    <n v="5787600010"/>
+    <s v="110/04"/>
+    <n v="67380"/>
+    <n v="346"/>
+    <x v="5"/>
+    <n v="110"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="011"/>
+    <n v="5787600010"/>
+    <s v="110/01"/>
+    <n v="68691"/>
+    <n v="346"/>
+    <x v="6"/>
+    <n v="110"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="012"/>
+    <n v="5787600010"/>
+    <s v="110/02"/>
+    <n v="64281"/>
+    <n v="346"/>
+    <x v="7"/>
+    <n v="110"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="014"/>
+    <n v="5787600010"/>
+    <s v="109/11"/>
+    <n v="66010"/>
+    <n v="346"/>
+    <x v="8"/>
+    <n v="109"/>
+    <n v="11"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="015"/>
+    <n v="5787600010"/>
+    <s v="109/12"/>
+    <n v="68353"/>
+    <n v="346"/>
+    <x v="9"/>
+    <n v="109"/>
+    <n v="12"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="017"/>
+    <n v="5787600010"/>
+    <s v="109/09"/>
+    <n v="86082"/>
+    <n v="346"/>
+    <x v="10"/>
+    <n v="109"/>
+    <n v="9"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="018"/>
+    <n v="5787600010"/>
+    <s v="109/10"/>
+    <n v="71742"/>
+    <n v="346"/>
+    <x v="11"/>
+    <n v="109"/>
+    <n v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="020"/>
+    <n v="5787600010"/>
+    <s v="109/07"/>
+    <n v="83856"/>
+    <n v="346"/>
+    <x v="12"/>
+    <n v="109"/>
+    <n v="7"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="021"/>
+    <n v="5787600010"/>
+    <s v="109/08"/>
+    <n v="77514"/>
+    <n v="346"/>
+    <x v="13"/>
+    <n v="109"/>
+    <n v="8"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="023"/>
+    <n v="5787600010"/>
+    <s v="109/05"/>
+    <n v="22120"/>
+    <n v="346"/>
+    <x v="14"/>
+    <n v="109"/>
+    <n v="5"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="024"/>
+    <n v="5787600010"/>
+    <s v="109/06"/>
+    <n v="55538"/>
+    <n v="346"/>
+    <x v="15"/>
+    <n v="109"/>
+    <n v="6"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="026"/>
+    <n v="5787600010"/>
+    <s v="109/03"/>
+    <n v="67927"/>
+    <n v="346"/>
+    <x v="16"/>
+    <n v="109"/>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="027"/>
+    <n v="5787600010"/>
+    <s v="109/04"/>
+    <n v="70732"/>
+    <n v="346"/>
+    <x v="17"/>
+    <n v="109"/>
+    <n v="4"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="029"/>
+    <n v="5787600010"/>
+    <s v="109/01"/>
+    <n v="69772"/>
+    <n v="346"/>
+    <x v="18"/>
+    <n v="109"/>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="030"/>
+    <n v="5787600010"/>
+    <s v="109/02"/>
+    <n v="78864"/>
+    <n v="346"/>
+    <x v="19"/>
+    <n v="109"/>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="001"/>
+    <n v="5787608007"/>
+    <s v="110/08"/>
+    <n v="5696"/>
+    <n v="39"/>
+    <x v="20"/>
+    <n v="110"/>
+    <n v="8"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="004"/>
+    <n v="5787608007"/>
+    <s v="110/06"/>
+    <n v="5347"/>
+    <n v="39"/>
+    <x v="21"/>
+    <n v="110"/>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="007"/>
+    <n v="5787608007"/>
+    <s v="110/04"/>
+    <n v="6131"/>
+    <n v="39"/>
+    <x v="22"/>
+    <n v="110"/>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="010"/>
+    <n v="5787608007"/>
+    <s v="110/02"/>
+    <n v="5043"/>
+    <n v="39"/>
+    <x v="23"/>
+    <n v="110"/>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="013"/>
+    <n v="5787608007"/>
+    <s v="109/12"/>
+    <n v="4862"/>
+    <n v="39"/>
+    <x v="24"/>
+    <n v="109"/>
+    <n v="12"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <s v="016"/>
+    <n v="5787608007"/>
+    <s v="109/10"/>
+    <n v="4325"/>
+    <n v="39"/>
+    <x v="25"/>
+    <n v="109"/>
+    <n v="10"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <s v="019"/>
+    <n v="5787608007"/>
+    <s v="109/08"/>
+    <n v="4201"/>
+    <n v="39"/>
+    <x v="26"/>
+    <n v="109"/>
+    <n v="8"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="022"/>
+    <n v="5787608007"/>
+    <s v="109/06"/>
+    <n v="3121"/>
+    <n v="39"/>
+    <x v="27"/>
+    <n v="109"/>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="025"/>
+    <n v="5787608007"/>
+    <s v="109/04"/>
+    <n v="6312"/>
+    <n v="39"/>
+    <x v="28"/>
+    <n v="109"/>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <s v="028"/>
     <n v="5787608007"/>
     <s v="109/02"/>
     <n v="10457"/>
     <n v="39"/>
-    <n v="268.10000000000002"/>
+    <x v="29"/>
+    <n v="109"/>
+    <n v="2"/>
     <x v="1"/>
-    <x v="7"/>
     <x v="1"/>
+    <x v="3"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{01862D7D-80D8-0D4F-8213-6FD9A2EB5D86}" name="樞紐分析表6" cacheId="48" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ECFEE284-8998-4847-8623-03E70B62DE01}" name="樞紐分析表7" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A47:D61" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0">
+      <items count="31">
+        <item x="14"/>
+        <item x="27"/>
+        <item x="26"/>
+        <item x="25"/>
+        <item x="24"/>
+        <item x="23"/>
+        <item x="21"/>
+        <item x="20"/>
+        <item x="22"/>
+        <item x="15"/>
+        <item x="28"/>
+        <item x="7"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="16"/>
+        <item x="9"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="11"/>
+        <item x="4"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="9"/>
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="8"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="加總 - 分攤金額" fld="5" baseField="0" baseItem="0" numFmtId="177"/>
+  </dataFields>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{01862D7D-80D8-0D4F-8213-6FD9A2EB5D86}" name="樞紐分析表6" cacheId="55" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:D27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="180" showAll="0"/>
-    <pivotField numFmtId="180" showAll="0"/>
-    <pivotField dataField="1" numFmtId="181" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField numFmtId="176" showAll="0"/>
+    <pivotField dataField="1" numFmtId="177" showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="1"/>
@@ -2481,8 +4651,8 @@
     </pivotField>
     <pivotField axis="axisCol" showAll="0">
       <items count="5">
+        <item m="1" x="3"/>
         <item m="1" x="2"/>
-        <item m="1" x="3"/>
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
@@ -2579,7 +4749,7 @@
     </i>
   </colItems>
   <dataFields count="1">
-    <dataField name="加總 - 分攤金額" fld="4" baseField="0" baseItem="0" numFmtId="181"/>
+    <dataField name="加總 - 分攤金額" fld="4" baseField="0" baseItem="0" numFmtId="177"/>
   </dataFields>
   <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
@@ -2964,7 +5134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35D83FA3-AC18-FD41-BFFB-0E92458C495A}">
-  <dimension ref="A3:G27"/>
+  <dimension ref="A3:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -2985,10 +5155,10 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
@@ -2999,25 +5169,25 @@
         <v>31</v>
       </c>
       <c r="B5" s="9">
-        <v>2794.6</v>
+        <v>2365.1</v>
       </c>
       <c r="C5" s="9">
-        <v>1121.2</v>
+        <v>853.1</v>
       </c>
       <c r="D5" s="9">
-        <v>3915.7999999999997</v>
+        <v>3218.1999999999994</v>
       </c>
       <c r="E5" s="9">
         <f>B5/12</f>
-        <v>232.88333333333333</v>
+        <v>197.09166666666667</v>
       </c>
       <c r="F5" s="9">
         <f>C5/12</f>
-        <v>93.433333333333337</v>
+        <v>71.091666666666669</v>
       </c>
       <c r="G5" s="9">
         <f>E5+F5</f>
-        <v>326.31666666666666</v>
+        <v>268.18333333333334</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3025,11 +5195,11 @@
         <v>33</v>
       </c>
       <c r="B6" s="9">
-        <v>403.2</v>
+        <v>201.6</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9">
-        <v>403.2</v>
+        <v>201.6</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3037,13 +5207,13 @@
         <v>34</v>
       </c>
       <c r="B7" s="9">
-        <v>455.8</v>
+        <v>227.9</v>
       </c>
       <c r="C7" s="9">
-        <v>536.20000000000005</v>
+        <v>268.10000000000002</v>
       </c>
       <c r="D7" s="9">
-        <v>992</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3311,25 +5481,411 @@
         <v>29</v>
       </c>
       <c r="B27" s="9">
-        <v>4398.2999999999993</v>
+        <v>3968.7999999999997</v>
       </c>
       <c r="C27" s="9">
-        <v>1690.8</v>
+        <v>1422.7</v>
       </c>
       <c r="D27" s="9">
-        <v>6089.0999999999985</v>
+        <v>5391.4999999999991</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="11">
+        <v>109</v>
+      </c>
+      <c r="B49" s="9">
+        <v>2365.1</v>
+      </c>
+      <c r="C49" s="9">
+        <v>853.1</v>
+      </c>
+      <c r="D49" s="9">
+        <v>3218.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="12">
+        <v>2</v>
+      </c>
+      <c r="B50" s="9">
+        <v>429.5</v>
+      </c>
+      <c r="C50" s="9">
+        <v>268.10000000000002</v>
+      </c>
+      <c r="D50" s="9">
+        <v>697.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="12">
+        <v>4</v>
+      </c>
+      <c r="B51" s="9">
+        <v>400.70000000000005</v>
+      </c>
+      <c r="C51" s="9">
+        <v>161.80000000000001</v>
+      </c>
+      <c r="D51" s="9">
+        <v>562.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="12">
+        <v>6</v>
+      </c>
+      <c r="B52" s="9">
+        <v>224.4</v>
+      </c>
+      <c r="C52" s="9">
+        <v>80</v>
+      </c>
+      <c r="D52" s="9">
+        <v>304.39999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="12">
+        <v>8</v>
+      </c>
+      <c r="B53" s="9">
+        <v>466.3</v>
+      </c>
+      <c r="C53" s="9">
+        <v>107.7</v>
+      </c>
+      <c r="D53" s="9">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="12">
+        <v>10</v>
+      </c>
+      <c r="B54" s="9">
+        <v>456</v>
+      </c>
+      <c r="C54" s="9">
+        <v>110.9</v>
+      </c>
+      <c r="D54" s="9">
+        <v>566.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="12">
+        <v>12</v>
+      </c>
+      <c r="B55" s="9">
+        <v>388.2</v>
+      </c>
+      <c r="C55" s="9">
+        <v>124.6</v>
+      </c>
+      <c r="D55" s="9">
+        <v>512.79999999999995</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="11">
+        <v>110</v>
+      </c>
+      <c r="B56" s="9">
+        <v>1603.6999999999998</v>
+      </c>
+      <c r="C56" s="9">
+        <v>569.6</v>
+      </c>
+      <c r="D56" s="9">
+        <v>2173.3000000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="12">
+        <v>2</v>
+      </c>
+      <c r="B57" s="9">
+        <v>384.2</v>
+      </c>
+      <c r="C57" s="9">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="D57" s="9">
+        <v>513.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="12">
+        <v>4</v>
+      </c>
+      <c r="B58" s="9">
+        <v>403.1</v>
+      </c>
+      <c r="C58" s="9">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="D58" s="9">
+        <v>560.29999999999995</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="12">
+        <v>6</v>
+      </c>
+      <c r="B59" s="9">
+        <v>388.5</v>
+      </c>
+      <c r="C59" s="9">
+        <v>137.1</v>
+      </c>
+      <c r="D59" s="9">
+        <v>525.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="12">
+        <v>8</v>
+      </c>
+      <c r="B60" s="9">
+        <v>427.9</v>
+      </c>
+      <c r="C60" s="9">
+        <v>146</v>
+      </c>
+      <c r="D60" s="9">
+        <v>573.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B61" s="9">
+        <v>3968.7999999999997</v>
+      </c>
+      <c r="C61" s="9">
+        <v>1422.7</v>
+      </c>
+      <c r="D61" s="9">
+        <v>5391.5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="B67" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" s="18">
+        <v>109</v>
+      </c>
+      <c r="C68" s="19">
+        <v>2365.1</v>
+      </c>
+      <c r="D68" s="19">
+        <v>853.1</v>
+      </c>
+      <c r="E68" s="19">
+        <v>3218.2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5">
+      <c r="B69" s="12">
+        <v>2</v>
+      </c>
+      <c r="C69" s="9">
+        <v>429.5</v>
+      </c>
+      <c r="D69" s="9">
+        <v>268.10000000000002</v>
+      </c>
+      <c r="E69" s="9">
+        <v>697.6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5">
+      <c r="B70" s="12">
+        <v>4</v>
+      </c>
+      <c r="C70" s="9">
+        <v>400.70000000000005</v>
+      </c>
+      <c r="D70" s="9">
+        <v>161.80000000000001</v>
+      </c>
+      <c r="E70" s="9">
+        <v>562.5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5">
+      <c r="B71" s="12">
+        <v>6</v>
+      </c>
+      <c r="C71" s="9">
+        <v>224.4</v>
+      </c>
+      <c r="D71" s="9">
+        <v>80</v>
+      </c>
+      <c r="E71" s="9">
+        <v>304.39999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5">
+      <c r="B72" s="12">
+        <v>8</v>
+      </c>
+      <c r="C72" s="9">
+        <v>466.3</v>
+      </c>
+      <c r="D72" s="9">
+        <v>107.7</v>
+      </c>
+      <c r="E72" s="9">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5">
+      <c r="B73" s="12">
+        <v>10</v>
+      </c>
+      <c r="C73" s="9">
+        <v>456</v>
+      </c>
+      <c r="D73" s="9">
+        <v>110.9</v>
+      </c>
+      <c r="E73" s="9">
+        <v>566.9</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="B74" s="12">
+        <v>12</v>
+      </c>
+      <c r="C74" s="9">
+        <v>388.2</v>
+      </c>
+      <c r="D74" s="9">
+        <v>124.6</v>
+      </c>
+      <c r="E74" s="9">
+        <v>512.79999999999995</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="B75" s="18">
+        <v>110</v>
+      </c>
+      <c r="C75" s="19">
+        <v>1603.6999999999998</v>
+      </c>
+      <c r="D75" s="19">
+        <v>569.6</v>
+      </c>
+      <c r="E75" s="19">
+        <v>2173.3000000000002</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="B76" s="12">
+        <v>2</v>
+      </c>
+      <c r="C76" s="9">
+        <v>384.2</v>
+      </c>
+      <c r="D76" s="9">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="E76" s="9">
+        <v>513.5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="B77" s="12">
+        <v>4</v>
+      </c>
+      <c r="C77" s="9">
+        <v>403.1</v>
+      </c>
+      <c r="D77" s="9">
+        <v>157.19999999999999</v>
+      </c>
+      <c r="E77" s="9">
+        <v>560.29999999999995</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5">
+      <c r="B78" s="12">
+        <v>6</v>
+      </c>
+      <c r="C78" s="9">
+        <v>388.5</v>
+      </c>
+      <c r="D78" s="9">
+        <v>137.1</v>
+      </c>
+      <c r="E78" s="9">
+        <v>525.6</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5">
+      <c r="B79" s="12">
+        <v>8</v>
+      </c>
+      <c r="C79" s="9">
+        <v>427.9</v>
+      </c>
+      <c r="D79" s="9">
+        <v>146</v>
+      </c>
+      <c r="E79" s="9">
+        <v>573.9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C053774A-6441-CA44-B623-21E8A72E1535}">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="14"/>
@@ -3338,7 +5894,7 @@
     <col min="6" max="6" width="11" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19">
+    <row r="1" spans="1:11" ht="19">
       <c r="A1" s="13" t="s">
         <v>46</v>
       </c>
@@ -3366,8 +5922,14 @@
       <c r="I1" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="19">
+      <c r="J1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="19">
       <c r="A2" s="13" t="s">
         <v>48</v>
       </c>
@@ -3386,19 +5948,23 @@
       <c r="F2" s="8">
         <v>201.5</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <f>LEFT(C2,3)</f>
+      <c r="G2" s="16">
         <v>110</v>
       </c>
-      <c r="H2" t="str">
-        <f>RIGHT(C2,2)</f>
-        <v>08</v>
+      <c r="H2" s="17">
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J2" s="16">
+        <v>110</v>
+      </c>
+      <c r="K2" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="19">
       <c r="A3" s="13" t="s">
         <v>49</v>
       </c>
@@ -3417,19 +5983,23 @@
       <c r="F3" s="8">
         <v>226.4</v>
       </c>
-      <c r="G3" s="2" t="str">
-        <f>LEFT(C3,3)</f>
+      <c r="G3" s="16">
         <v>110</v>
       </c>
-      <c r="H3" t="str">
-        <f>RIGHT(C3,2)</f>
-        <v>07</v>
+      <c r="H3" s="17">
+        <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J3" s="16">
+        <v>110</v>
+      </c>
+      <c r="K3" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="19">
       <c r="A4" s="13" t="s">
         <v>51</v>
       </c>
@@ -3448,19 +6018,23 @@
       <c r="F4" s="8">
         <v>187.8</v>
       </c>
-      <c r="G4" s="2" t="str">
-        <f>LEFT(C4,3)</f>
+      <c r="G4" s="16">
         <v>110</v>
       </c>
-      <c r="H4" t="str">
-        <f>RIGHT(C4,2)</f>
-        <v>05</v>
+      <c r="H4" s="17">
+        <v>5</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J4" s="16">
+        <v>110</v>
+      </c>
+      <c r="K4" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="19">
       <c r="A5" s="13" t="s">
         <v>52</v>
       </c>
@@ -3479,19 +6053,23 @@
       <c r="F5" s="8">
         <v>200.7</v>
       </c>
-      <c r="G5" s="2" t="str">
-        <f>LEFT(C5,3)</f>
+      <c r="G5" s="16">
         <v>110</v>
       </c>
-      <c r="H5" t="str">
-        <f>RIGHT(C5,2)</f>
-        <v>06</v>
+      <c r="H5" s="17">
+        <v>6</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J5" s="16">
+        <v>110</v>
+      </c>
+      <c r="K5" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="19">
       <c r="A6" s="13" t="s">
         <v>54</v>
       </c>
@@ -3510,19 +6088,23 @@
       <c r="F6" s="8">
         <v>208.4</v>
       </c>
-      <c r="G6" s="2" t="str">
-        <f>LEFT(C6,3)</f>
+      <c r="G6" s="16">
         <v>110</v>
       </c>
-      <c r="H6" t="str">
-        <f>RIGHT(C6,2)</f>
-        <v>03</v>
+      <c r="H6" s="17">
+        <v>3</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J6" s="16">
+        <v>110</v>
+      </c>
+      <c r="K6" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="19">
       <c r="A7" s="13" t="s">
         <v>55</v>
       </c>
@@ -3541,19 +6123,23 @@
       <c r="F7" s="8">
         <v>194.7</v>
       </c>
-      <c r="G7" s="2" t="str">
-        <f>LEFT(C7,3)</f>
+      <c r="G7" s="16">
         <v>110</v>
       </c>
-      <c r="H7" t="str">
-        <f>RIGHT(C7,2)</f>
-        <v>04</v>
+      <c r="H7" s="17">
+        <v>4</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J7" s="16">
+        <v>110</v>
+      </c>
+      <c r="K7" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="19">
       <c r="A8" s="13" t="s">
         <v>57</v>
       </c>
@@ -3572,19 +6158,23 @@
       <c r="F8" s="8">
         <v>198.5</v>
       </c>
-      <c r="G8" s="2" t="str">
-        <f>LEFT(C8,3)</f>
+      <c r="G8" s="16">
         <v>110</v>
       </c>
-      <c r="H8" t="str">
-        <f>RIGHT(C8,2)</f>
-        <v>01</v>
+      <c r="H8" s="17">
+        <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J8" s="16">
+        <v>110</v>
+      </c>
+      <c r="K8" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="19">
       <c r="A9" s="13" t="s">
         <v>58</v>
       </c>
@@ -3603,19 +6193,23 @@
       <c r="F9" s="8">
         <v>185.7</v>
       </c>
-      <c r="G9" s="2" t="str">
-        <f>LEFT(C9,3)</f>
+      <c r="G9" s="16">
         <v>110</v>
       </c>
-      <c r="H9" t="str">
-        <f>RIGHT(C9,2)</f>
-        <v>02</v>
+      <c r="H9" s="17">
+        <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J9" s="16">
+        <v>110</v>
+      </c>
+      <c r="K9" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19">
       <c r="A10" s="13" t="s">
         <v>60</v>
       </c>
@@ -3634,19 +6228,23 @@
       <c r="F10" s="8">
         <v>190.7</v>
       </c>
-      <c r="G10" s="2" t="str">
-        <f>LEFT(C10,3)</f>
+      <c r="G10" s="16">
         <v>109</v>
       </c>
-      <c r="H10" t="str">
-        <f>RIGHT(C10,2)</f>
+      <c r="H10" s="17">
         <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J10" s="16">
+        <v>109</v>
+      </c>
+      <c r="K10" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19">
       <c r="A11" s="13" t="s">
         <v>61</v>
       </c>
@@ -3665,19 +6263,23 @@
       <c r="F11" s="8">
         <v>197.5</v>
       </c>
-      <c r="G11" s="2" t="str">
-        <f>LEFT(C11,3)</f>
+      <c r="G11" s="16">
         <v>109</v>
       </c>
-      <c r="H11" t="str">
-        <f>RIGHT(C11,2)</f>
+      <c r="H11" s="17">
         <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J11" s="16">
+        <v>109</v>
+      </c>
+      <c r="K11" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="19">
       <c r="A12" s="13" t="s">
         <v>63</v>
       </c>
@@ -3696,19 +6298,23 @@
       <c r="F12" s="8">
         <v>248.7</v>
       </c>
-      <c r="G12" s="2" t="str">
-        <f>LEFT(C12,3)</f>
+      <c r="G12" s="16">
         <v>109</v>
       </c>
-      <c r="H12" t="str">
-        <f>RIGHT(C12,2)</f>
-        <v>09</v>
+      <c r="H12" s="17">
+        <v>9</v>
       </c>
       <c r="I12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J12" s="16">
+        <v>109</v>
+      </c>
+      <c r="K12" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="19">
       <c r="A13" s="13" t="s">
         <v>64</v>
       </c>
@@ -3727,19 +6333,23 @@
       <c r="F13" s="8">
         <v>207.3</v>
       </c>
-      <c r="G13" s="2" t="str">
-        <f>LEFT(C13,3)</f>
+      <c r="G13" s="16">
         <v>109</v>
       </c>
-      <c r="H13" t="str">
-        <f>RIGHT(C13,2)</f>
+      <c r="H13" s="17">
         <v>10</v>
       </c>
       <c r="I13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J13" s="16">
+        <v>109</v>
+      </c>
+      <c r="K13" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="19">
       <c r="A14" s="13" t="s">
         <v>66</v>
       </c>
@@ -3758,19 +6368,23 @@
       <c r="F14" s="8">
         <v>242.3</v>
       </c>
-      <c r="G14" s="2" t="str">
-        <f>LEFT(C14,3)</f>
+      <c r="G14" s="16">
         <v>109</v>
       </c>
-      <c r="H14" t="str">
-        <f>RIGHT(C14,2)</f>
-        <v>07</v>
+      <c r="H14" s="17">
+        <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J14" s="16">
+        <v>109</v>
+      </c>
+      <c r="K14" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="19">
       <c r="A15" s="13" t="s">
         <v>67</v>
       </c>
@@ -3789,19 +6403,23 @@
       <c r="F15" s="8">
         <v>224</v>
       </c>
-      <c r="G15" s="2" t="str">
-        <f>LEFT(C15,3)</f>
+      <c r="G15" s="16">
         <v>109</v>
       </c>
-      <c r="H15" t="str">
-        <f>RIGHT(C15,2)</f>
-        <v>08</v>
+      <c r="H15" s="17">
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J15" s="16">
+        <v>109</v>
+      </c>
+      <c r="K15" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19">
       <c r="A16" s="13" t="s">
         <v>69</v>
       </c>
@@ -3820,19 +6438,23 @@
       <c r="F16" s="8">
         <v>63.9</v>
       </c>
-      <c r="G16" s="2" t="str">
-        <f>LEFT(C16,3)</f>
+      <c r="G16" s="16">
         <v>109</v>
       </c>
-      <c r="H16" t="str">
-        <f>RIGHT(C16,2)</f>
-        <v>05</v>
+      <c r="H16" s="17">
+        <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J16" s="16">
+        <v>109</v>
+      </c>
+      <c r="K16" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="19">
       <c r="A17" s="13" t="s">
         <v>70</v>
       </c>
@@ -3851,19 +6473,23 @@
       <c r="F17" s="8">
         <v>160.5</v>
       </c>
-      <c r="G17" s="2" t="str">
-        <f>LEFT(C17,3)</f>
+      <c r="G17" s="16">
         <v>109</v>
       </c>
-      <c r="H17" t="str">
-        <f>RIGHT(C17,2)</f>
-        <v>06</v>
+      <c r="H17" s="17">
+        <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J17" s="16">
+        <v>109</v>
+      </c>
+      <c r="K17" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="19">
       <c r="A18" s="13" t="s">
         <v>72</v>
       </c>
@@ -3882,19 +6508,23 @@
       <c r="F18" s="8">
         <v>196.3</v>
       </c>
-      <c r="G18" s="2" t="str">
-        <f>LEFT(C18,3)</f>
+      <c r="G18" s="16">
         <v>109</v>
       </c>
-      <c r="H18" t="str">
-        <f>RIGHT(C18,2)</f>
-        <v>03</v>
+      <c r="H18" s="17">
+        <v>3</v>
       </c>
       <c r="I18" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J18" s="16">
+        <v>109</v>
+      </c>
+      <c r="K18" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="19">
       <c r="A19" s="13" t="s">
         <v>73</v>
       </c>
@@ -3913,19 +6543,23 @@
       <c r="F19" s="8">
         <v>204.4</v>
       </c>
-      <c r="G19" s="2" t="str">
-        <f>LEFT(C19,3)</f>
+      <c r="G19" s="16">
         <v>109</v>
       </c>
-      <c r="H19" t="str">
-        <f>RIGHT(C19,2)</f>
-        <v>04</v>
+      <c r="H19" s="17">
+        <v>4</v>
       </c>
       <c r="I19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J19" s="16">
+        <v>109</v>
+      </c>
+      <c r="K19" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="19">
       <c r="A20" s="13" t="s">
         <v>75</v>
       </c>
@@ -3944,19 +6578,23 @@
       <c r="F20" s="8">
         <v>201.6</v>
       </c>
-      <c r="G20" s="2" t="str">
-        <f>LEFT(C20,3)</f>
+      <c r="G20" s="16">
         <v>109</v>
       </c>
-      <c r="H20" t="str">
-        <f>RIGHT(C20,2)</f>
-        <v>01</v>
+      <c r="H20" s="17">
+        <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J20" s="16">
+        <v>109</v>
+      </c>
+      <c r="K20" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="19">
       <c r="A21" s="13" t="s">
         <v>76</v>
       </c>
@@ -3975,478 +6613,426 @@
       <c r="F21" s="8">
         <v>227.9</v>
       </c>
-      <c r="G21" s="2" t="str">
-        <f>LEFT(C21,3)</f>
+      <c r="G21" s="16">
         <v>109</v>
       </c>
-      <c r="H21" t="str">
-        <f>RIGHT(C21,2)</f>
-        <v>02</v>
+      <c r="H21" s="17">
+        <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="19">
+        <v>78</v>
+      </c>
+      <c r="J21" s="16">
+        <v>109</v>
+      </c>
+      <c r="K21" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="19">
       <c r="A22" s="13" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1">
-        <v>5787600010</v>
+        <v>5787608007</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5">
-        <v>69772</v>
+        <v>5696</v>
       </c>
       <c r="E22" s="5">
-        <v>346</v>
+        <v>39</v>
       </c>
       <c r="F22" s="8">
-        <v>201.6</v>
-      </c>
-      <c r="G22" s="2" t="str">
-        <f>LEFT(C22,3)</f>
-        <v>109</v>
-      </c>
-      <c r="H22" t="str">
-        <f>RIGHT(C22,2)</f>
-        <v>01</v>
+        <v>146</v>
+      </c>
+      <c r="G22" s="16">
+        <v>110</v>
+      </c>
+      <c r="H22" s="17">
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J22" s="16">
+        <v>110</v>
+      </c>
+      <c r="K22" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="19">
       <c r="A23" s="13" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1">
-        <v>5787600010</v>
+        <v>5787608007</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D23" s="5">
-        <v>78864</v>
+        <v>5347</v>
       </c>
       <c r="E23" s="5">
-        <v>346</v>
+        <v>39</v>
       </c>
       <c r="F23" s="8">
-        <v>227.9</v>
-      </c>
-      <c r="G23" s="2" t="str">
-        <f>LEFT(C23,3)</f>
-        <v>109</v>
-      </c>
-      <c r="H23" t="str">
-        <f>RIGHT(C23,2)</f>
-        <v>02</v>
+        <v>137.1</v>
+      </c>
+      <c r="G23" s="16">
+        <v>110</v>
+      </c>
+      <c r="H23" s="17">
+        <v>6</v>
       </c>
       <c r="I23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J23" s="16">
+        <v>110</v>
+      </c>
+      <c r="K23" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="19">
       <c r="A24" s="13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1">
         <v>5787608007</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D24" s="5">
-        <v>5696</v>
+        <v>6131</v>
       </c>
       <c r="E24" s="5">
         <v>39</v>
       </c>
       <c r="F24" s="8">
-        <v>146</v>
-      </c>
-      <c r="G24" s="2" t="str">
-        <f>LEFT(C24,3)</f>
+        <v>157.19999999999999</v>
+      </c>
+      <c r="G24" s="16">
         <v>110</v>
       </c>
-      <c r="H24" t="str">
-        <f>RIGHT(C24,2)</f>
-        <v>08</v>
+      <c r="H24" s="17">
+        <v>4</v>
       </c>
       <c r="I24" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J24" s="16">
+        <v>110</v>
+      </c>
+      <c r="K24" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="19">
       <c r="A25" s="13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1">
         <v>5787608007</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D25" s="5">
-        <v>5347</v>
+        <v>5043</v>
       </c>
       <c r="E25" s="5">
         <v>39</v>
       </c>
       <c r="F25" s="8">
-        <v>137.1</v>
-      </c>
-      <c r="G25" s="2" t="str">
-        <f>LEFT(C25,3)</f>
+        <v>129.30000000000001</v>
+      </c>
+      <c r="G25" s="16">
         <v>110</v>
       </c>
-      <c r="H25" t="str">
-        <f>RIGHT(C25,2)</f>
-        <v>06</v>
+      <c r="H25" s="17">
+        <v>2</v>
       </c>
       <c r="I25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J25" s="16">
+        <v>110</v>
+      </c>
+      <c r="K25" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="19">
       <c r="A26" s="13" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1">
         <v>5787608007</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5">
-        <v>6131</v>
+        <v>4862</v>
       </c>
       <c r="E26" s="5">
         <v>39</v>
       </c>
       <c r="F26" s="8">
-        <v>157.19999999999999</v>
-      </c>
-      <c r="G26" s="2" t="str">
-        <f>LEFT(C26,3)</f>
-        <v>110</v>
-      </c>
-      <c r="H26" t="str">
-        <f>RIGHT(C26,2)</f>
-        <v>04</v>
+        <v>124.6</v>
+      </c>
+      <c r="G26" s="16">
+        <v>109</v>
+      </c>
+      <c r="H26" s="17">
+        <v>12</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J26" s="16">
+        <v>109</v>
+      </c>
+      <c r="K26" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="19">
       <c r="A27" s="13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1">
         <v>5787608007</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D27" s="5">
-        <v>5043</v>
+        <v>4325</v>
       </c>
       <c r="E27" s="5">
         <v>39</v>
       </c>
       <c r="F27" s="8">
-        <v>129.30000000000001</v>
-      </c>
-      <c r="G27" s="2" t="str">
-        <f>LEFT(C27,3)</f>
-        <v>110</v>
-      </c>
-      <c r="H27" t="str">
-        <f>RIGHT(C27,2)</f>
-        <v>02</v>
+        <v>110.9</v>
+      </c>
+      <c r="G27" s="16">
+        <v>109</v>
+      </c>
+      <c r="H27" s="17">
+        <v>10</v>
       </c>
       <c r="I27" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J27" s="16">
+        <v>109</v>
+      </c>
+      <c r="K27" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="19">
       <c r="A28" s="13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B28" s="1">
         <v>5787608007</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D28" s="5">
-        <v>4862</v>
+        <v>4201</v>
       </c>
       <c r="E28" s="5">
         <v>39</v>
       </c>
       <c r="F28" s="8">
-        <v>124.6</v>
-      </c>
-      <c r="G28" s="2" t="str">
-        <f>LEFT(C28,3)</f>
+        <v>107.7</v>
+      </c>
+      <c r="G28" s="16">
         <v>109</v>
       </c>
-      <c r="H28" t="str">
-        <f>RIGHT(C28,2)</f>
-        <v>12</v>
+      <c r="H28" s="17">
+        <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J28" s="16">
+        <v>109</v>
+      </c>
+      <c r="K28" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="19">
       <c r="A29" s="13" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1">
         <v>5787608007</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D29" s="5">
-        <v>4325</v>
+        <v>3121</v>
       </c>
       <c r="E29" s="5">
         <v>39</v>
       </c>
       <c r="F29" s="8">
-        <v>110.9</v>
-      </c>
-      <c r="G29" s="2" t="str">
-        <f>LEFT(C29,3)</f>
+        <v>80</v>
+      </c>
+      <c r="G29" s="16">
         <v>109</v>
       </c>
-      <c r="H29" t="str">
-        <f>RIGHT(C29,2)</f>
-        <v>10</v>
+      <c r="H29" s="17">
+        <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J29" s="16">
+        <v>109</v>
+      </c>
+      <c r="K29" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="19">
       <c r="A30" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1">
         <v>5787608007</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D30" s="5">
-        <v>4201</v>
+        <v>6312</v>
       </c>
       <c r="E30" s="5">
         <v>39</v>
       </c>
       <c r="F30" s="8">
-        <v>107.7</v>
-      </c>
-      <c r="G30" s="2" t="str">
-        <f>LEFT(C30,3)</f>
+        <v>161.80000000000001</v>
+      </c>
+      <c r="G30" s="16">
         <v>109</v>
       </c>
-      <c r="H30" t="str">
-        <f>RIGHT(C30,2)</f>
-        <v>08</v>
+      <c r="H30" s="17">
+        <v>4</v>
       </c>
       <c r="I30" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="19">
+        <v>80</v>
+      </c>
+      <c r="J30" s="16">
+        <v>109</v>
+      </c>
+      <c r="K30" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="19">
       <c r="A31" s="13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B31" s="1">
         <v>5787608007</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D31" s="5">
-        <v>3121</v>
+        <v>10457</v>
       </c>
       <c r="E31" s="5">
         <v>39</v>
       </c>
       <c r="F31" s="8">
+        <v>268.10000000000002</v>
+      </c>
+      <c r="G31" s="16">
+        <v>109</v>
+      </c>
+      <c r="H31" s="17">
+        <v>2</v>
+      </c>
+      <c r="I31" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="2" t="str">
-        <f>LEFT(C31,3)</f>
+      <c r="J31" s="16">
         <v>109</v>
       </c>
-      <c r="H31" t="str">
-        <f>RIGHT(C31,2)</f>
-        <v>06</v>
-      </c>
-      <c r="I31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="19">
-      <c r="A32" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="1">
-        <v>5787608007</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="5">
-        <v>6312</v>
-      </c>
-      <c r="E32" s="5">
-        <v>39</v>
-      </c>
-      <c r="F32" s="8">
-        <v>161.80000000000001</v>
-      </c>
-      <c r="G32" s="2" t="str">
-        <f>LEFT(C32,3)</f>
-        <v>109</v>
-      </c>
-      <c r="H32" t="str">
-        <f>RIGHT(C32,2)</f>
-        <v>04</v>
-      </c>
-      <c r="I32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="19">
-      <c r="A33" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1">
-        <v>5787608007</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="5">
-        <v>10457</v>
-      </c>
-      <c r="E33" s="5">
-        <v>39</v>
-      </c>
-      <c r="F33" s="8">
-        <v>268.10000000000002</v>
-      </c>
-      <c r="G33" s="2" t="str">
-        <f>LEFT(C33,3)</f>
-        <v>109</v>
-      </c>
-      <c r="H33" t="str">
-        <f>RIGHT(C33,2)</f>
-        <v>02</v>
-      </c>
-      <c r="I33" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="19">
-      <c r="A34" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="1">
-        <v>5787608007</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="5">
-        <v>10457</v>
-      </c>
-      <c r="E34" s="5">
-        <v>39</v>
-      </c>
-      <c r="F34" s="8">
-        <v>268.10000000000002</v>
-      </c>
-      <c r="G34" s="2" t="str">
-        <f>LEFT(C34,3)</f>
-        <v>109</v>
-      </c>
-      <c r="H34" t="str">
-        <f>RIGHT(C34,2)</f>
-        <v>02</v>
-      </c>
-      <c r="I34" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="19">
-      <c r="A35" s="13"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:9" ht="19">
-      <c r="A36" s="13"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="2"/>
+      <c r="K31" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="19">
+      <c r="A32" s="13"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" ht="19">
+      <c r="A33" s="13"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I34">
-    <sortCondition ref="B2:B34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I31">
+    <sortCondition ref="B2:B31"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B24" r:id="rId1" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc7u5ESnqLOVx52SdA19DR5mA7rmNS2nQogMiEiVmOgLr" xr:uid="{183AA61A-E364-9A4C-A831-A6CC3B0B1E2B}"/>
+    <hyperlink ref="B22" r:id="rId1" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc7u5ESnqLOVx52SdA19DR5mA7rmNS2nQogMiEiVmOgLr" xr:uid="{183AA61A-E364-9A4C-A831-A6CC3B0B1E2B}"/>
     <hyperlink ref="B2" r:id="rId2" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcxK7yXtE0OYSWeq8*zR%2B5TzfcT8L4xYr10YYpYOUOB9c" xr:uid="{09D7364E-249A-034D-AEE7-B1392723B3E7}"/>
     <hyperlink ref="B3" r:id="rId3" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc1*eulvQbUnQZ01MLRsK*goujKEaNPfE5UgqnU%2BxSFWI" xr:uid="{9A0197A9-07FE-8045-93EF-6B231A4B9A0E}"/>
-    <hyperlink ref="B25" r:id="rId4" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcxA5lw4GJvtdJi2xdBJ1TFnWfG9s%2BWUeXF9UmghT3Sl6" xr:uid="{16992929-DEDA-1C42-AA2B-712D96E4C1B6}"/>
+    <hyperlink ref="B23" r:id="rId4" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcxA5lw4GJvtdJi2xdBJ1TFnWfG9s%2BWUeXF9UmghT3Sl6" xr:uid="{16992929-DEDA-1C42-AA2B-712D96E4C1B6}"/>
     <hyperlink ref="B4" r:id="rId5" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc*0iB4yc1voW3lonHAkQiPrdiW*eEY*nDA0t1fv6sdGe" xr:uid="{29F96556-9361-EE41-B68D-C93D93EABAC6}"/>
     <hyperlink ref="B5" r:id="rId6" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc7D8G2UcVLhcea8zq3zFdJfC7q1bOa3OCV81tne7oQQL" xr:uid="{E6EF8DEF-0AF0-5543-B42D-A5B1F24D4702}"/>
-    <hyperlink ref="B26" r:id="rId7" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc0gHbIbR6nXjryYfi2%2BYtwVwPWPxUls3vRS2EH6QHEkC" xr:uid="{04A2A363-C678-AA4D-B484-E827921FEEB8}"/>
+    <hyperlink ref="B24" r:id="rId7" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc0gHbIbR6nXjryYfi2%2BYtwVwPWPxUls3vRS2EH6QHEkC" xr:uid="{04A2A363-C678-AA4D-B484-E827921FEEB8}"/>
     <hyperlink ref="B6" r:id="rId8" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcyuShRQASX7q2yF3Ng6PkpvNl0iDyPVakC7D77hr4MyG" xr:uid="{D41B36B6-F670-5147-B6B4-C3DBDFDF52F2}"/>
     <hyperlink ref="B7" r:id="rId9" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc43w4BxMkR*AamuH71YtUgQ6MlIQu6O2CQ1c1kppr0RL" xr:uid="{86602C9E-0E7A-5945-A6D4-9D4D4A160ED3}"/>
-    <hyperlink ref="B27" r:id="rId10" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc*A0bvv01IJ6rHt8aw5nZTClZbeMypTs%2BOdoGuvdts%2BA" xr:uid="{4B2E193C-A5F1-6940-B099-F24BF66783A9}"/>
+    <hyperlink ref="B25" r:id="rId10" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc*A0bvv01IJ6rHt8aw5nZTClZbeMypTs%2BOdoGuvdts%2BA" xr:uid="{4B2E193C-A5F1-6940-B099-F24BF66783A9}"/>
     <hyperlink ref="B8" r:id="rId11" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc%2BB0RAN7qXIuKZIq1eKBGZiEpZJ5rlukfMQUvMsx8cJm" xr:uid="{9CFB41B0-424F-344F-9EB1-8FE136881C2A}"/>
     <hyperlink ref="B9" r:id="rId12" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcx56d7w4TKEtuLUUA82s6YFLDnlH0YlSJX1wkaYCI03O" xr:uid="{49D67E43-B29A-A945-A1A9-CE775D9B3113}"/>
-    <hyperlink ref="B28" r:id="rId13" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc0t%2BFytb6DfwijgdC0jx10*D5meoOnzOmWHBop3XGKOx" xr:uid="{501699CA-5F6C-0746-A369-B511EECC0CAF}"/>
+    <hyperlink ref="B26" r:id="rId13" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc0t%2BFytb6DfwijgdC0jx10*D5meoOnzOmWHBop3XGKOx" xr:uid="{501699CA-5F6C-0746-A369-B511EECC0CAF}"/>
     <hyperlink ref="B10" r:id="rId14" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc6EUu1ncTsidVhGiI5NUwJ0895p%2Bo%2BU0t9an7fxjFoLR" xr:uid="{FB192B19-92CB-ED4F-A8A1-FDED7F3FF6F6}"/>
     <hyperlink ref="B11" r:id="rId15" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc3*vLaQcV1j8qgLmzub3Mt5pt7wqalr9pTxCPmlDRZSJ" xr:uid="{85FA7A82-34AF-AF49-9896-0DA55031F667}"/>
-    <hyperlink ref="B29" r:id="rId16" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc%2BMtj%2BYIxuQImcMXgv9zRMpF5AkPNDCzpmIfMUG0zKJ1" xr:uid="{EE80A818-A0B3-FA4A-9ACE-0B3BD2EC6652}"/>
+    <hyperlink ref="B27" r:id="rId16" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc%2BMtj%2BYIxuQImcMXgv9zRMpF5AkPNDCzpmIfMUG0zKJ1" xr:uid="{EE80A818-A0B3-FA4A-9ACE-0B3BD2EC6652}"/>
     <hyperlink ref="B12" r:id="rId17" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc8xKMVDSa%2BzC1Z0utSBa5A4PUNaAaROn8Mrr3yyGAJGW" xr:uid="{A995AF24-A2D4-D74B-80B7-575894388A94}"/>
     <hyperlink ref="B13" r:id="rId18" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc3ZWECcH%2BDX4XRQ1%2BP2L7PRLVgeWwE%2BxHdft5rLXnK*K" xr:uid="{982B2E9F-1358-8949-8F55-936E0EE6DF65}"/>
-    <hyperlink ref="B30" r:id="rId19" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc3DJTKPj1rML6gpY*6aeS3rBcRwOwOeI1jR%2Budh4tJwZ" xr:uid="{07667651-EBC1-8148-879B-7D44F2AA77E6}"/>
+    <hyperlink ref="B28" r:id="rId19" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc3DJTKPj1rML6gpY*6aeS3rBcRwOwOeI1jR%2Budh4tJwZ" xr:uid="{07667651-EBC1-8148-879B-7D44F2AA77E6}"/>
     <hyperlink ref="B14" r:id="rId20" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc%2BIs3hFOmEIohmFw0W*g*eq0s2vtU*x17GnZC3kLY6zf" xr:uid="{754832F3-8336-1649-A174-CB54119B66FD}"/>
     <hyperlink ref="B15" r:id="rId21" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc2%2BmOIffifTt1HZLQHWxn9teV6Tlf2ww%2BGJJOueoOi7V" xr:uid="{54474269-5C0B-9B48-A479-F86FD16B01D7}"/>
-    <hyperlink ref="B31" r:id="rId22" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcx2rASkZ4ZnL70ioqGXwoOZHbkVPgYcmy2WscsCNqPPH" xr:uid="{6283C7DE-38AF-C04B-80B0-92F6169340DC}"/>
+    <hyperlink ref="B29" r:id="rId22" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcx2rASkZ4ZnL70ioqGXwoOZHbkVPgYcmy2WscsCNqPPH" xr:uid="{6283C7DE-38AF-C04B-80B0-92F6169340DC}"/>
     <hyperlink ref="B16" r:id="rId23" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc9DB8DDWEXhSBjt2y5yBczGu0ZKBLBPX6WhMZKuXTuyK" xr:uid="{3FDC9CBA-7D55-F44A-B8E9-45BA09871D09}"/>
     <hyperlink ref="B17" r:id="rId24" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpczs5RYYbR9xQpojTIKm23u6x7V*EhRJeNW5hVR5aL8aN" xr:uid="{9824D8D0-C4CC-C841-9E0C-F6F5DEF103EE}"/>
-    <hyperlink ref="B32" r:id="rId25" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcwvtkA1HdYAmm09wg1MrpwIDzqZhhmQJVbF0TjoacZJT" xr:uid="{6B9B6342-BFE9-7945-985A-6C840AA25299}"/>
+    <hyperlink ref="B30" r:id="rId25" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcwvtkA1HdYAmm09wg1MrpwIDzqZhhmQJVbF0TjoacZJT" xr:uid="{6B9B6342-BFE9-7945-985A-6C840AA25299}"/>
     <hyperlink ref="B18" r:id="rId26" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc1B8gus4%2ByFqdAHJ%2BkVXu9YInj95dGjXRqnHg5O%2BnlT*" xr:uid="{35587899-2691-B746-B2F8-424C8DC56782}"/>
     <hyperlink ref="B19" r:id="rId27" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcwc%2BlGPa8nWZX9gEo9jVMRtMYCqv9DrHONlzdHR4lSDj" xr:uid="{07971C13-7546-514B-8533-4AC49CA10AE3}"/>
-    <hyperlink ref="B33" r:id="rId28" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc9HTVnxFeAOxMtji5MM*B6i*s86Jy9%2BfhiS*8BvnITJi" xr:uid="{F70823E2-9EF1-C740-A17C-B97D02B53D42}"/>
+    <hyperlink ref="B31" r:id="rId28" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc9HTVnxFeAOxMtji5MM*B6i*s86Jy9%2BfhiS*8BvnITJi" xr:uid="{F70823E2-9EF1-C740-A17C-B97D02B53D42}"/>
     <hyperlink ref="B20" r:id="rId29" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc0fi0eXLYkvcDtjuiYkVAUgAj8yX52asmo*Vk2120TKi" xr:uid="{52E882CC-7134-0344-8384-FE1394E8D528}"/>
     <hyperlink ref="B21" r:id="rId30" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcw9NVV0MmX89MUy3OjYw9b5fa4TJKblVM73lZvax4T*f" xr:uid="{690DC3F6-2B36-6F46-9E6F-29EBC183674C}"/>
-    <hyperlink ref="B34" r:id="rId31" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc9HTVnxFeAOxMtji5MM*B6i*s86Jy9%2BfhiS*8BvnITJi" xr:uid="{3CBC6781-E479-EE4B-B7A0-59EBE2C287AC}"/>
-    <hyperlink ref="B22" r:id="rId32" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpc0fi0eXLYkvcDtjuiYkVAUgAj8yX52asmo*Vk2120TKi" xr:uid="{17B4B9C9-227E-024E-B465-8F261AA2CA4F}"/>
-    <hyperlink ref="B23" r:id="rId33" display="https://ebpps2.taipower.com.tw/bill/myebill-detail-publicno/L/2D0jV1tjDXxe3vWCeCGpcw9NVV0MmX89MUy3OjYw9b5fa4TJKblVM73lZvax4T*f" xr:uid="{7C570425-DA79-3140-9BC2-5EA23448F10E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
